--- a/output/pdf_financials_xlsx/HYTN.xlsx
+++ b/output/pdf_financials_xlsx/HYTN.xlsx
@@ -1900,13 +1900,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.002776</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.002776</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.002776</v>
       </c>
     </row>
     <row r="93">
@@ -3362,7 +3362,11 @@
           <t>Warrant reserve 12</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>0.002776</v>
       </c>

--- a/output/pdf_financials_xlsx/HYTN.xlsx
+++ b/output/pdf_financials_xlsx/HYTN.xlsx
@@ -964,13 +964,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.187559</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.25658</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.344515</v>
       </c>
     </row>
     <row r="35">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.187559</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.25658</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.344515</v>
       </c>
     </row>
     <row r="37">
@@ -1188,13 +1188,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.192559</v>
+        <v>0.005</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.277168</v>
+        <v>0.020588</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.352404</v>
+        <v>0.007889</v>
       </c>
     </row>
     <row r="49">
@@ -2406,7 +2406,7 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D124" s="3" t="n">
         <v>0</v>
@@ -2422,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="D125" s="3" t="n">
         <v>0</v>
@@ -2694,7 +2694,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -4485,7 +4485,11 @@
           <t>Repayment of indebtedness 10</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HYTN.xlsx
+++ b/output/pdf_financials_xlsx/HYTN.xlsx
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="B110" s="3" t="n">
-        <v>0</v>
+        <v>0.132775</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.146638</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.134331</v>
       </c>
     </row>
     <row r="111">
@@ -3819,7 +3819,11 @@
           <t>Interest/accretion expense 8,9</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
         <v>0.132775</v>
       </c>
